--- a/Electrical-Hardware-Design-H2-Sensor-Board/H2-Sensor-Board2024_Sally/H2-Sensor-Board/ADC_pinout_plan.xlsx
+++ b/Electrical-Hardware-Design-H2-Sensor-Board/H2-Sensor-Board2024_Sally/H2-Sensor-Board/ADC_pinout_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\owang\Sally-Electrical-Design\Electrical-Hardware-Design-H2-Sensor-Board\H2-Sensor-Board2024_Sally\H2-Sensor-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E23C7A7-799E-4B72-ACA7-10FDD13E6354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C18E3B7-6734-4898-BFC6-62F3A3958695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28845" yWindow="4515" windowWidth="14295" windowHeight="10365" xr2:uid="{3CE88FCB-CC4D-4EEC-B49E-07699882D789}"/>
   </bookViews>
